--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -206,16 +206,25 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CORDOVA</t>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
   </si>
   <si>
     <t>HUERTA</t>
@@ -224,16 +233,22 @@
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>IAN</t>
   </si>
   <si>
     <t>JOSE LUIS</t>
   </si>
   <si>
     <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
   </si>
 </sst>
 </file>
@@ -763,16 +778,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -852,16 +867,16 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -894,7 +909,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -903,7 +918,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -941,16 +956,16 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -986,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <v>8</v>
@@ -1030,16 +1045,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1081,7 +1096,7 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1119,16 +1134,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1161,7 +1176,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1208,16 +1223,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1259,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1297,16 +1312,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1386,16 +1401,16 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1437,7 +1452,7 @@
         <v>6</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1475,16 +1490,16 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1520,13 +1535,13 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1564,16 +1579,16 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1609,7 +1624,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1653,16 +1668,16 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1742,16 +1757,16 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1831,16 +1846,16 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1873,10 +1888,10 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -1920,16 +1935,16 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1965,7 +1980,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>6</v>
@@ -2009,16 +2024,16 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2051,10 +2066,10 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -2098,16 +2113,16 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2143,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2187,16 +2202,16 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2232,13 +2247,13 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2276,16 +2291,16 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2318,7 +2333,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2327,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2365,16 +2380,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2407,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2454,16 +2469,16 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2499,13 +2514,13 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -2543,16 +2558,16 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2632,16 +2647,16 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2674,16 +2689,16 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>10</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>10</v>
@@ -2721,16 +2736,16 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2810,16 +2825,16 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2852,7 +2867,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -3021,7 +3036,7 @@
         <v>80</v>
       </c>
       <c r="J4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="K4">
         <v>90</v>
@@ -3030,7 +3045,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>87.5</v>
@@ -3042,7 +3057,7 @@
         <v>80</v>
       </c>
       <c r="Q4">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R4">
         <v>90</v>
@@ -3051,7 +3066,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U4">
         <v>87.5</v>
@@ -3089,16 +3104,16 @@
         <v>80</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N5">
         <v>93.8</v>
@@ -3110,16 +3125,16 @@
         <v>80</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="S5">
         <v>100</v>
       </c>
       <c r="T5">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U5">
         <v>93.8</v>
@@ -3166,7 +3181,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3187,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3228,13 +3243,13 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3249,13 +3264,13 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3293,10 +3308,10 @@
         <v>80</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K8">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3314,10 +3329,10 @@
         <v>80</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3432,13 +3447,13 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3453,13 +3468,13 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -3497,16 +3512,16 @@
         <v>80</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N11">
         <v>93.8</v>
@@ -3518,16 +3533,16 @@
         <v>80</v>
       </c>
       <c r="Q11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U11">
         <v>93.8</v>
@@ -3633,16 +3648,16 @@
         <v>90</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N13">
         <v>93.8</v>
@@ -3654,16 +3669,16 @@
         <v>90</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S13">
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U13">
         <v>93.8</v>
@@ -3701,7 +3716,7 @@
         <v>80</v>
       </c>
       <c r="J14">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="K14">
         <v>90</v>
@@ -3710,7 +3725,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="N14">
         <v>93.8</v>
@@ -3722,7 +3737,7 @@
         <v>80</v>
       </c>
       <c r="Q14">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="R14">
         <v>90</v>
@@ -3731,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="U14">
         <v>93.8</v>
@@ -3769,10 +3784,10 @@
         <v>80</v>
       </c>
       <c r="J15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3790,10 +3805,10 @@
         <v>80</v>
       </c>
       <c r="Q15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3840,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3861,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3905,10 +3920,10 @@
         <v>90</v>
       </c>
       <c r="J17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3926,10 +3941,10 @@
         <v>90</v>
       </c>
       <c r="Q17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3973,16 +3988,16 @@
         <v>80</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K18">
+        <v>97.5</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>95</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
       </c>
       <c r="N18">
         <v>87.5</v>
@@ -3994,16 +4009,16 @@
         <v>80</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R18">
+        <v>97.5</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>95</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>100</v>
       </c>
       <c r="U18">
         <v>87.5</v>
@@ -4044,13 +4059,13 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4065,13 +4080,13 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4112,7 +4127,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4133,7 +4148,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4177,7 +4192,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4198,7 +4213,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4248,13 +4263,13 @@
         <v>86.7</v>
       </c>
       <c r="K22">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N22">
         <v>87.5</v>
@@ -4269,13 +4284,13 @@
         <v>86.7</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U22">
         <v>87.5</v>
@@ -4381,7 +4396,7 @@
         <v>80</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4390,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N24">
         <v>87.5</v>
@@ -4402,7 +4417,7 @@
         <v>80</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4411,7 +4426,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U24">
         <v>87.5</v>
@@ -4520,7 +4535,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4541,7 +4556,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4585,16 +4600,16 @@
         <v>80</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K27">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -4606,16 +4621,16 @@
         <v>80</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R27">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -4687,19 +4702,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="G2" s="2">
-        <v>62.5</v>
+        <v>58.3</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4731,7 +4746,7 @@
         <v>54.2</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4751,19 +4766,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="G4" s="2">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4961,7 +4976,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4993,16 +5008,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920030</v>
+        <v>23330051920033</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5016,16 +5031,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920030</v>
+        <v>23330051920033</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5039,22 +5054,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920038</v>
+        <v>23330051920043</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5062,16 +5077,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920038</v>
+        <v>23330051920043</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5091,10 +5106,10 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5111,13 +5126,13 @@
         <v>23330051920037</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5126,6 +5141,29 @@
         <v>50</v>
       </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920039</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>LOBATO</t>
   </si>
   <si>
-    <t>DURAND</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
   </si>
   <si>
     <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
   </si>
   <si>
     <t>IAN</t>
@@ -784,16 +775,16 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -832,7 +823,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -873,16 +864,16 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -921,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -962,16 +953,16 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1004,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1013,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1051,16 +1042,16 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1093,7 +1084,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1140,16 +1131,16 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1188,10 +1179,10 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1229,16 +1220,16 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1277,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1318,16 +1309,16 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1360,13 +1351,13 @@
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1407,16 +1398,16 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1449,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>6</v>
@@ -1496,16 +1487,16 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1538,7 +1529,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1547,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1585,16 +1576,16 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1627,16 +1618,16 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1674,16 +1665,16 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1716,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1725,7 +1716,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1763,16 +1754,16 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1811,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1852,16 +1843,16 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1900,10 +1891,10 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1941,16 +1932,16 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1983,16 +1974,16 @@
         <v>5</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2030,16 +2021,16 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2072,13 +2063,13 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2119,16 +2110,16 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2161,13 +2152,13 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2208,16 +2199,16 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2297,16 +2288,16 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2386,16 +2377,16 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2428,13 +2419,13 @@
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2475,16 +2466,16 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2523,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2564,16 +2555,16 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2653,16 +2644,16 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2701,7 +2692,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2742,16 +2733,16 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2784,16 +2775,16 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2831,16 +2822,16 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2879,10 +2870,10 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3048,7 +3039,7 @@
         <v>90</v>
       </c>
       <c r="N4">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O4">
         <v>90</v>
@@ -3069,7 +3060,7 @@
         <v>90</v>
       </c>
       <c r="U4">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V4">
         <v>90</v>
@@ -3116,10 +3107,10 @@
         <v>82.5</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="O5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P5">
         <v>80</v>
@@ -3137,10 +3128,10 @@
         <v>82.5</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V5">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3252,10 +3243,10 @@
         <v>97.5</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
         <v>80</v>
@@ -3273,10 +3264,10 @@
         <v>97.5</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3320,10 +3311,10 @@
         <v>80</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P8">
         <v>80</v>
@@ -3341,10 +3332,10 @@
         <v>80</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3456,7 +3447,7 @@
         <v>82.5</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3477,7 +3468,7 @@
         <v>82.5</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3527,7 +3518,7 @@
         <v>93.8</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P11">
         <v>80</v>
@@ -3548,7 +3539,7 @@
         <v>93.8</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3592,7 +3583,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
         <v>95</v>
@@ -3613,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V12">
         <v>95</v>
@@ -3660,10 +3651,10 @@
         <v>90</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
         <v>90</v>
@@ -3681,10 +3672,10 @@
         <v>90</v>
       </c>
       <c r="U13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3728,10 +3719,10 @@
         <v>65</v>
       </c>
       <c r="N14">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="P14">
         <v>80</v>
@@ -3749,10 +3740,10 @@
         <v>65</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3796,10 +3787,10 @@
         <v>80</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P15">
         <v>80</v>
@@ -3817,10 +3808,10 @@
         <v>80</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V15">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3867,7 +3858,7 @@
         <v>93.8</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P16">
         <v>90</v>
@@ -3888,7 +3879,7 @@
         <v>93.8</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3932,10 +3923,10 @@
         <v>80</v>
       </c>
       <c r="N17">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P17">
         <v>90</v>
@@ -3953,10 +3944,10 @@
         <v>80</v>
       </c>
       <c r="U17">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4000,10 +3991,10 @@
         <v>95</v>
       </c>
       <c r="N18">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P18">
         <v>80</v>
@@ -4021,10 +4012,10 @@
         <v>95</v>
       </c>
       <c r="U18">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4204,7 +4195,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4225,7 +4216,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4272,10 +4263,10 @@
         <v>85</v>
       </c>
       <c r="N22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P22">
         <v>80</v>
@@ -4293,10 +4284,10 @@
         <v>85</v>
       </c>
       <c r="U22">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V22">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4408,7 +4399,7 @@
         <v>97.5</v>
       </c>
       <c r="N24">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O24">
         <v>90</v>
@@ -4429,7 +4420,7 @@
         <v>97.5</v>
       </c>
       <c r="U24">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V24">
         <v>90</v>
@@ -4544,10 +4535,10 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
         <v>80</v>
@@ -4565,10 +4556,10 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4615,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P27">
         <v>80</v>
@@ -4636,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -4798,19 +4789,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4830,19 +4821,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="G6" s="2">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4894,19 +4885,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>91.7</v>
+        <v>87.5</v>
       </c>
       <c r="G8" s="2">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4976,7 +4967,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5008,22 +4999,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920033</v>
+        <v>23330051920043</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5031,22 +5022,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920033</v>
+        <v>23330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5054,22 +5045,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920043</v>
+        <v>23330051920035</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5077,16 +5068,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920043</v>
+        <v>23330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5100,16 +5091,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920035</v>
+        <v>23330051920039</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5118,52 +5109,6 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920037</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920039</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -766,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -855,7 +855,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>7</v>
@@ -897,7 +897,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -944,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1033,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1122,7 +1122,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1164,7 +1164,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1342,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1389,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1431,7 +1431,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1478,7 +1478,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1520,7 +1520,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1567,7 +1567,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1656,7 +1656,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1787,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1834,7 +1834,7 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1923,7 +1923,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -2012,7 +2012,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>7</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2101,7 +2101,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2190,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>8</v>
@@ -2279,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2321,7 +2321,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2368,7 +2368,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>7</v>
@@ -2410,7 +2410,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2457,7 +2457,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -2499,7 +2499,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2546,7 +2546,7 @@
         <v>4</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2588,7 +2588,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2635,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2724,7 +2724,7 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2766,7 +2766,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2813,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -3228,7 +3228,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3249,7 +3249,7 @@
         <v>97.5</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3432,7 +3432,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3453,7 +3453,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3500,7 +3500,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>90</v>
@@ -3521,7 +3521,7 @@
         <v>97.5</v>
       </c>
       <c r="P11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q11">
         <v>90</v>
@@ -3568,7 +3568,7 @@
         <v>95</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3589,7 +3589,7 @@
         <v>95</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3908,7 +3908,7 @@
         <v>85</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J17">
         <v>90</v>
@@ -3929,7 +3929,7 @@
         <v>87.5</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q17">
         <v>90</v>
@@ -3976,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <v>93.3</v>
@@ -3997,7 +3997,7 @@
         <v>97.5</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q18">
         <v>93.3</v>
@@ -4248,7 +4248,7 @@
         <v>95</v>
       </c>
       <c r="I22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>86.7</v>
@@ -4269,7 +4269,7 @@
         <v>92.5</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q22">
         <v>86.7</v>
@@ -4384,7 +4384,7 @@
         <v>90</v>
       </c>
       <c r="I24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J24">
         <v>93.3</v>
@@ -4405,7 +4405,7 @@
         <v>90</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q24">
         <v>93.3</v>
@@ -4520,7 +4520,7 @@
         <v>95</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4541,7 +4541,7 @@
         <v>97.5</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4853,19 +4853,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="G7" s="2">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -3491,7 +3491,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G11">
         <v>93.8</v>
@@ -3512,7 +3512,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="N11">
         <v>93.8</v>
@@ -3533,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="U11">
         <v>93.8</v>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -206,40 +206,67 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
   </si>
   <si>
     <t>IAN</t>
   </si>
   <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JAZIEL</t>
+    <t>YAEL ISSAI</t>
   </si>
 </sst>
 </file>
@@ -790,22 +817,22 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -823,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -879,22 +906,22 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -903,19 +930,19 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -968,22 +995,22 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1057,28 +1084,28 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1146,22 +1173,22 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1182,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1235,22 +1262,22 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1262,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1324,34 +1351,34 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1413,40 +1440,40 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>7</v>
@@ -1502,22 +1529,22 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1529,16 +1556,16 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1591,22 +1618,22 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1680,22 +1707,22 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1769,22 +1796,22 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1796,16 +1823,16 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1858,37 +1885,37 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -1947,22 +1974,22 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2036,22 +2063,22 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2063,13 +2090,13 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2125,22 +2152,22 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2149,10 +2176,10 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2214,22 +2241,22 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2303,22 +2330,22 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2327,7 +2354,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>10</v>
@@ -2392,22 +2419,22 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2416,16 +2443,16 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2481,22 +2508,22 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2508,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2570,22 +2597,22 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2597,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2606,7 +2633,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2659,43 +2686,43 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>9</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2748,31 +2775,31 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -2781,10 +2808,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2837,28 +2864,28 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2870,10 +2897,10 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3048,22 +3075,22 @@
         <v>80</v>
       </c>
       <c r="Q4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U4">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3116,22 +3143,22 @@
         <v>80</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R5">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
+        <v>82.3</v>
+      </c>
+      <c r="U5">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="V5">
         <v>87.5</v>
-      </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
-        <v>82.5</v>
-      </c>
-      <c r="U5">
-        <v>87.5</v>
-      </c>
-      <c r="V5">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3193,7 +3220,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3255,19 +3282,19 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>97.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3320,7 +3347,7 @@
         <v>80</v>
       </c>
       <c r="Q8">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R8">
         <v>87.5</v>
@@ -3329,13 +3356,13 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>80</v>
+        <v>75.8</v>
       </c>
       <c r="U8">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V8">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3397,7 +3424,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3459,16 +3486,16 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>82.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3524,22 +3551,22 @@
         <v>85</v>
       </c>
       <c r="Q11">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R11">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>93.5</v>
       </c>
       <c r="U11">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3592,10 +3619,10 @@
         <v>95</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3604,10 +3631,10 @@
         <v>100</v>
       </c>
       <c r="U12">
+        <v>95.8</v>
+      </c>
+      <c r="V12">
         <v>96.90000000000001</v>
-      </c>
-      <c r="V12">
-        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3660,22 +3687,22 @@
         <v>90</v>
       </c>
       <c r="Q13">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
       </c>
       <c r="T13">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U13">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3728,22 +3755,22 @@
         <v>80</v>
       </c>
       <c r="Q14">
-        <v>83.3</v>
+        <v>70.8</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>65</v>
+        <v>48.4</v>
       </c>
       <c r="U14">
-        <v>87.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V14">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3796,22 +3823,22 @@
         <v>80</v>
       </c>
       <c r="Q15">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R15">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>74.2</v>
       </c>
       <c r="U15">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V15">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3867,19 +3894,19 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U16">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3932,22 +3959,22 @@
         <v>85</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>81.3</v>
       </c>
       <c r="R17">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>80</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U17">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V17">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4000,22 +4027,22 @@
         <v>85</v>
       </c>
       <c r="Q18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95</v>
+        <v>90.3</v>
       </c>
       <c r="U18">
         <v>93.8</v>
       </c>
       <c r="V18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4071,19 +4098,19 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>97.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4139,13 +4166,13 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -4204,7 +4231,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4213,10 +4240,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U21">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4272,22 +4299,22 @@
         <v>85</v>
       </c>
       <c r="Q22">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R22">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U22">
         <v>93.8</v>
       </c>
       <c r="V22">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4349,7 +4376,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -4408,7 +4435,7 @@
         <v>85</v>
       </c>
       <c r="Q24">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4417,13 +4444,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>97.5</v>
+        <v>93.5</v>
       </c>
       <c r="U24">
-        <v>84.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="V24">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4485,10 +4512,10 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4547,19 +4574,19 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="U26">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4612,22 +4639,22 @@
         <v>80</v>
       </c>
       <c r="Q27">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="R27">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="U27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V27">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4725,19 +4752,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>45.8</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>54.2</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4757,16 +4784,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>58.3</v>
+        <v>70.8</v>
       </c>
       <c r="G4" s="2">
-        <v>41.7</v>
+        <v>29.2</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -4780,7 +4807,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4789,19 +4816,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="G5" s="2">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4821,16 +4848,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="G6" s="2">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -4844,7 +4871,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4853,19 +4880,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G7" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4885,19 +4912,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4967,7 +4994,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4999,16 +5026,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920043</v>
+        <v>23330051920030</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5022,16 +5049,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920043</v>
+        <v>23330051920030</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5045,16 +5072,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920035</v>
+        <v>23330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5068,16 +5095,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920037</v>
+        <v>23330051920035</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5091,16 +5118,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920039</v>
+        <v>23330051920032</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5109,6 +5136,75 @@
         <v>50</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920039</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920043</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920046</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -179,10 +179,10 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
@@ -814,7 +814,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -903,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1170,7 +1170,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1259,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1348,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1437,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1526,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1615,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1793,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -1814,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1882,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -1971,7 +1971,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -1992,7 +1992,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2060,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2327,7 +2327,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2416,7 +2416,7 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2437,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2505,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2594,7 +2594,7 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2683,7 +2683,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2772,7 +2772,7 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2861,7 +2861,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -3072,7 +3072,7 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q4">
         <v>93.8</v>
@@ -3140,7 +3140,7 @@
         <v>80</v>
       </c>
       <c r="P5">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q5">
         <v>91.7</v>
@@ -3276,7 +3276,7 @@
         <v>97.5</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3344,7 +3344,7 @@
         <v>90</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q8">
         <v>89.59999999999999</v>
@@ -3480,7 +3480,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3548,7 +3548,7 @@
         <v>97.5</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q11">
         <v>93.8</v>
@@ -3616,7 +3616,7 @@
         <v>95</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q12">
         <v>97.90000000000001</v>
@@ -3684,7 +3684,7 @@
         <v>97.5</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q13">
         <v>93.8</v>
@@ -3752,7 +3752,7 @@
         <v>87.5</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q14">
         <v>70.8</v>
@@ -3820,7 +3820,7 @@
         <v>85</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q15">
         <v>87.5</v>
@@ -3888,7 +3888,7 @@
         <v>95</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3956,7 +3956,7 @@
         <v>87.5</v>
       </c>
       <c r="P17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q17">
         <v>81.3</v>
@@ -4024,7 +4024,7 @@
         <v>97.5</v>
       </c>
       <c r="P18">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q18">
         <v>95.8</v>
@@ -4296,7 +4296,7 @@
         <v>92.5</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q22">
         <v>91.7</v>
@@ -4432,7 +4432,7 @@
         <v>90</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q24">
         <v>95.8</v>
@@ -4568,7 +4568,7 @@
         <v>97.5</v>
       </c>
       <c r="P26">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4636,7 +4636,7 @@
         <v>97.5</v>
       </c>
       <c r="P27">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q27">
         <v>83.3</v>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4828,7 +4828,7 @@
         <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4848,19 +4848,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G6" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -165,9 +168,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -628,13 +628,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AG27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -645,35 +645,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,77 +703,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -793,7 +809,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -802,10 +818,10 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -817,48 +833,60 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>5</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>6</v>
+      </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -882,72 +910,84 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>7</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>8</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD5">
+        <v>5</v>
+      </c>
+      <c r="AE5">
+        <v>7</v>
+      </c>
+      <c r="AF5">
+        <v>6</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -971,72 +1011,84 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>10</v>
       </c>
       <c r="P6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>9</v>
       </c>
       <c r="S6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>9</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>6</v>
+      </c>
+      <c r="AE6">
+        <v>10</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1060,34 +1112,34 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>8</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1096,36 +1148,48 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>9</v>
+      </c>
+      <c r="AF7">
+        <v>8</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1149,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1173,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -1185,19 +1249,19 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1206,15 +1270,27 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>5</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1238,7 +1314,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1247,31 +1323,31 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>9</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1280,30 +1356,42 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>9</v>
+      </c>
+      <c r="AE9">
+        <v>9</v>
+      </c>
+      <c r="AF9">
+        <v>10</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1327,72 +1415,84 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>6</v>
       </c>
       <c r="L10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>6</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>5</v>
+      </c>
+      <c r="AE10">
+        <v>8</v>
+      </c>
+      <c r="AF10">
+        <v>8</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -1416,19 +1516,19 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>7</v>
@@ -1440,48 +1540,60 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>9</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>7</v>
+      </c>
+      <c r="AE11">
+        <v>8</v>
+      </c>
+      <c r="AF11">
+        <v>7</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1505,72 +1617,84 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>8</v>
+      </c>
+      <c r="AE12">
+        <v>8</v>
+      </c>
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1594,7 +1718,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1603,63 +1727,75 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>7</v>
       </c>
       <c r="S13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD13">
+        <v>5</v>
+      </c>
+      <c r="AE13">
+        <v>8</v>
+      </c>
+      <c r="AF13">
+        <v>8</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1707,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>5</v>
@@ -1731,7 +1867,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1745,10 +1881,22 @@
       <c r="AC14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>5</v>
+      </c>
+      <c r="AE14">
+        <v>5</v>
+      </c>
+      <c r="AF14">
+        <v>5</v>
+      </c>
+      <c r="AG14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1772,16 +1920,16 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
       <c r="K15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1793,34 +1941,34 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -1829,15 +1977,27 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>6</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -1861,72 +2021,84 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>7</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N16">
+        <v>6</v>
+      </c>
+      <c r="O16">
         <v>4</v>
       </c>
-      <c r="O16">
-        <v>8</v>
-      </c>
       <c r="P16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD16">
+        <v>6</v>
+      </c>
+      <c r="AE16">
+        <v>7</v>
+      </c>
+      <c r="AF16">
+        <v>7</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -1950,19 +2122,19 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -1971,51 +2143,63 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD17">
+        <v>5</v>
+      </c>
+      <c r="AE17">
+        <v>8</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -2039,7 +2223,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>7</v>
@@ -2048,63 +2232,75 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>7</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD18">
+        <v>5</v>
+      </c>
+      <c r="AE18">
+        <v>8</v>
+      </c>
+      <c r="AF18">
+        <v>7</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>8</v>
@@ -2128,37 +2324,37 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2167,33 +2363,45 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>7</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19">
+        <v>7</v>
+      </c>
+      <c r="AE19">
+        <v>9</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -2217,40 +2425,40 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>8</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>9</v>
       </c>
       <c r="O20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>10</v>
       </c>
       <c r="Q20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2259,30 +2467,42 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>10</v>
+      </c>
+      <c r="AF20">
+        <v>10</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -2309,13 +2529,13 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>9</v>
       </c>
       <c r="L21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2330,31 +2550,31 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>10</v>
@@ -2363,15 +2583,27 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>9</v>
+      </c>
+      <c r="AE21">
+        <v>10</v>
+      </c>
+      <c r="AF21">
+        <v>10</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -2395,72 +2627,84 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>7</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
+        <v>7</v>
+      </c>
+      <c r="AF22">
+        <v>6</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>9</v>
@@ -2487,69 +2731,81 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>8</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
       </c>
       <c r="N23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD23">
+        <v>9</v>
+      </c>
+      <c r="AE23">
+        <v>9</v>
+      </c>
+      <c r="AF23">
+        <v>10</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2573,58 +2829,58 @@
         <v>4</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
       <c r="L24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2633,12 +2889,24 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>6</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -2662,7 +2930,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2671,63 +2939,75 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>7</v>
       </c>
       <c r="O25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>6</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>6</v>
+      </c>
+      <c r="AE25">
+        <v>9</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2751,72 +3031,84 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>6</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>7</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD26">
+        <v>5</v>
+      </c>
+      <c r="AE26">
+        <v>8</v>
+      </c>
+      <c r="AF26">
+        <v>7</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -2840,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2858,16 +3150,16 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>5</v>
@@ -2882,33 +3174,45 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
+        <v>7</v>
+      </c>
+      <c r="AF27">
+        <v>6</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2916,16 +3220,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2933,26 +3237,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2978,56 +3285,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -3051,51 +3367,60 @@
         <v>90</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>80</v>
-      </c>
-      <c r="J4">
-        <v>90</v>
       </c>
       <c r="K4">
         <v>90</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>90</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>90.59999999999999</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>90</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>81.3</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>93.8</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>92.2</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>87.09999999999999</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>91.7</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>80</v>
@@ -3119,51 +3444,60 @@
         <v>85</v>
       </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>80</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>90</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>87.5</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>82.5</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>87.5</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>80</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>84.40000000000001</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>91.7</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>89.09999999999999</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
         <v>82.3</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>89.59999999999999</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -3199,11 +3533,11 @@
         <v>100</v>
       </c>
       <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
         <v>90</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
       <c r="O6">
         <v>100</v>
       </c>
@@ -3220,18 +3554,27 @@
         <v>100</v>
       </c>
       <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
         <v>87.09999999999999</v>
       </c>
-      <c r="U6">
-        <v>100</v>
-      </c>
-      <c r="V6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -3255,51 +3598,60 @@
         <v>100</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>85</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>95</v>
       </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
         <v>97.5</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>96.90000000000001</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>97.5</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>87.5</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>96.90000000000001</v>
       </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
         <v>91.90000000000001</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>97.90000000000001</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>80</v>
@@ -3323,51 +3675,60 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>80</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>93.3</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>87.5</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
         <v>80</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>90.59999999999999</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>90</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>81.3</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>89.59999999999999</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>87.5</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>75.8</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>89.59999999999999</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -3424,18 +3785,27 @@
         <v>100</v>
       </c>
       <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>96.8</v>
       </c>
-      <c r="U9">
-        <v>100</v>
-      </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9">
+        <v>100</v>
+      </c>
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>80</v>
@@ -3459,51 +3829,60 @@
         <v>100</v>
       </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>85</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>95</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
       <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
         <v>82.5</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>96.90000000000001</v>
       </c>
-      <c r="O10">
-        <v>100</v>
-      </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>87.5</v>
       </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>96.90000000000001</v>
       </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
         <v>83.90000000000001</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>97.90000000000001</v>
       </c>
-      <c r="V10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>80</v>
@@ -3527,51 +3906,60 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>85</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>90</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>92.5</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>95</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>93.8</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>97.5</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>87.5</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>93.8</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>93.8</v>
       </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
         <v>93.5</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>95.8</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -3595,11 +3983,11 @@
         <v>95</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>95</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
         <v>100</v>
       </c>
@@ -3610,36 +3998,45 @@
         <v>100</v>
       </c>
       <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
         <v>96.90000000000001</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>95</v>
       </c>
-      <c r="P12">
-        <v>96.90000000000001</v>
-      </c>
       <c r="Q12">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>96.90000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>95.8</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -3663,51 +4060,60 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>90</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>93.3</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>95</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>90</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>96.90000000000001</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>97.5</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90.59999999999999</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>93.8</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>96.90000000000001</v>
       </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>87.09999999999999</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>95.8</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>80</v>
@@ -3731,51 +4137,60 @@
         <v>95</v>
       </c>
       <c r="I14">
+        <v>33.3</v>
+      </c>
+      <c r="J14">
         <v>80</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>83.3</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>90</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
         <v>65</v>
-      </c>
-      <c r="N14">
-        <v>87.5</v>
       </c>
       <c r="O14">
         <v>87.5</v>
       </c>
       <c r="P14">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="Q14">
-        <v>70.8</v>
+        <v>66.7</v>
       </c>
       <c r="R14">
         <v>84.40000000000001</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>70.8</v>
       </c>
       <c r="T14">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
         <v>48.4</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>64.59999999999999</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>80</v>
@@ -3799,51 +4214,60 @@
         <v>90</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>80</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>90</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>95</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
       <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
         <v>80</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>96.90000000000001</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>85</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>81.3</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>87.5</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>92.2</v>
       </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-      <c r="T15">
+      <c r="U15">
+        <v>100</v>
+      </c>
+      <c r="V15">
         <v>74.2</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>91.7</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>90.59999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>90</v>
@@ -3867,51 +4291,60 @@
         <v>100</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>90</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>97.5</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>93.8</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>95</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>90.59999999999999</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>98.40000000000001</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
         <v>96.8</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>91.7</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -3935,51 +4368,60 @@
         <v>85</v>
       </c>
       <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
         <v>85</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>90</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>97.5</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
         <v>80</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>84.40000000000001</v>
-      </c>
-      <c r="O17">
-        <v>87.5</v>
       </c>
       <c r="P17">
         <v>87.5</v>
       </c>
       <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>87.5</v>
+      </c>
+      <c r="S17">
         <v>81.3</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>93.8</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
         <v>83.90000000000001</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>87.5</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -4003,51 +4445,60 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>85</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>93.3</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>97.5</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
         <v>95</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>93.8</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>97.5</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>87.5</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>95.8</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>98.40000000000001</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>90.3</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>93.8</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -4077,45 +4528,54 @@
         <v>100</v>
       </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>92.5</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>97.5</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>90</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>95.3</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
         <v>91.90000000000001</v>
       </c>
-      <c r="U19">
-        <v>100</v>
-      </c>
-      <c r="V19">
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -4145,11 +4605,11 @@
         <v>100</v>
       </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>97.5</v>
       </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
         <v>100</v>
       </c>
@@ -4166,24 +4626,33 @@
         <v>100</v>
       </c>
       <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>98.40000000000001</v>
       </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
         <v>96.8</v>
       </c>
-      <c r="U20">
-        <v>100</v>
-      </c>
-      <c r="V20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="W20">
+        <v>100</v>
+      </c>
+      <c r="X20">
+        <v>100</v>
+      </c>
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -4210,11 +4679,11 @@
         <v>100</v>
       </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>93.3</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
       <c r="L21">
         <v>100</v>
       </c>
@@ -4222,36 +4691,45 @@
         <v>100</v>
       </c>
       <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
         <v>96.90000000000001</v>
       </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
         <v>95.8</v>
       </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
-      <c r="S21">
-        <v>100</v>
-      </c>
       <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
         <v>96.8</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>97.90000000000001</v>
       </c>
-      <c r="V21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="X21">
+        <v>100</v>
+      </c>
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -4275,51 +4753,60 @@
         <v>95</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>85</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>86.7</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>87.5</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>85</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>93.8</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>92.5</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>90.59999999999999</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>91.7</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>92.2</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>87.09999999999999</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>93.8</v>
       </c>
-      <c r="V22">
+      <c r="X22">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -4376,18 +4863,27 @@
         <v>100</v>
       </c>
       <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
         <v>96.8</v>
       </c>
-      <c r="U23">
-        <v>100</v>
-      </c>
-      <c r="V23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="W23">
+        <v>100</v>
+      </c>
+      <c r="X23">
+        <v>100</v>
+      </c>
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -4411,51 +4907,60 @@
         <v>90</v>
       </c>
       <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>85</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>93.3</v>
       </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
         <v>97.5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>84.40000000000001</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>90</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>84.40000000000001</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>95.8</v>
       </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
       <c r="T24">
+        <v>100</v>
+      </c>
+      <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
         <v>93.5</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>62.5</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -4512,18 +5017,27 @@
         <v>100</v>
       </c>
       <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
         <v>96.8</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>97.90000000000001</v>
       </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -4547,51 +5061,60 @@
         <v>95</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>85</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>97.5</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>96.90000000000001</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>97.5</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>87.5</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>98.40000000000001</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
         <v>96.8</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>95.8</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>80</v>
@@ -4615,53 +5138,62 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>80</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>93.3</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>92.5</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
       <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
         <v>90</v>
       </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
       <c r="O27">
+        <v>100</v>
+      </c>
+      <c r="P27">
         <v>97.5</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>84.40000000000001</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>83.3</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>95.3</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-      <c r="T27">
+      <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
         <v>79</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>93.8</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>98.40000000000001</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4682,31 +5214,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4935,21 +5467,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
       </c>
       <c r="C9">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>95.8</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="H9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4984,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5018,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -869,13 +869,13 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -961,25 +961,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1062,19 +1062,19 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6">
         <v>10</v>
@@ -1163,25 +1163,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD7">
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1365,22 +1365,22 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1466,25 +1466,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1567,25 +1567,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1668,25 +1668,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1769,25 +1769,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD13">
         <v>5</v>
       </c>
       <c r="AE13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1971,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA15">
         <v>5</v>
@@ -1980,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2072,25 +2072,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2173,7 +2173,7 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2182,13 +2182,13 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD17">
         <v>5</v>
       </c>
       <c r="AE17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2274,25 +2274,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD18">
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2375,25 +2375,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2476,19 +2476,19 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>10</v>
       </c>
       <c r="AD20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE20">
         <v>10</v>
@@ -2580,16 +2580,16 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>10</v>
       </c>
       <c r="AD21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE21">
         <v>10</v>
@@ -2678,25 +2678,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2779,22 +2779,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>10</v>
@@ -2880,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2889,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>5</v>
@@ -2898,7 +2898,7 @@
         <v>5</v>
       </c>
       <c r="AF24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2981,25 +2981,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3082,25 +3082,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD26">
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -3198,10 +3198,10 @@
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -5264,7 +5264,7 @@
         <v>58.3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5296,7 +5296,7 @@
         <v>33.3</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>29.2</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>12.5</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>12.5</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5456,7 +5456,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1BM - Estadisticos 20231.xlsx
+++ b/grupos/1BM - Estadisticos 20231.xlsx
@@ -869,13 +869,13 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -961,25 +961,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD5">
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1062,19 +1062,19 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>10</v>
@@ -1163,25 +1163,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1365,22 +1365,22 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1466,25 +1466,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1567,25 +1567,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1668,25 +1668,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1769,25 +1769,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD13">
         <v>5</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1971,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>5</v>
@@ -1980,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2072,25 +2072,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2173,7 +2173,7 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2182,13 +2182,13 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD17">
         <v>5</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2274,25 +2274,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD18">
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2375,25 +2375,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2476,19 +2476,19 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>10</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>10</v>
@@ -2580,16 +2580,16 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>10</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE21">
         <v>10</v>
@@ -2678,25 +2678,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2779,22 +2779,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF23">
         <v>10</v>
@@ -2880,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2889,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD24">
         <v>5</v>
@@ -2898,7 +2898,7 @@
         <v>5</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2981,25 +2981,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3082,25 +3082,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD26">
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -3198,10 +3198,10 @@
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -5264,7 +5264,7 @@
         <v>58.3</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5296,7 +5296,7 @@
         <v>33.3</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>29.2</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>16.7</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>12.5</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>12.5</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5456,7 +5456,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H8">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
